--- a/Purchase Register Format.xlsx
+++ b/Purchase Register Format.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="7" rupBuild="4507"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\projects\trust tea\tracetea_revamp\data_mtb_git\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A870953-FDD9-4FFD-8392-0F855DEB53C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="-105" windowWidth="19425" windowHeight="10305"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Data" sheetId="1" r:id="rId1"/>
@@ -37,9 +43,6 @@
     <t>3717  -</t>
   </si>
   <si>
-    <t>Vendor</t>
-  </si>
-  <si>
     <t>Vendor Name</t>
   </si>
   <si>
@@ -765,16 +768,19 @@
   </si>
   <si>
     <t>Project/Asset PO</t>
+  </si>
+  <si>
+    <t>Vendor(vendor_code)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="#,##0.000"/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1217,20 +1223,20 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:FJ7"/>
-  <sheetFormatPr defaultRowHeight="12.75" outlineLevelRow="1"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" outlineLevelRow="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="19" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="45" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.109375" style="1" customWidth="1"/>
     <col min="4" max="4" width="15" style="1" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="38" style="1" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="17" style="1" bestFit="1" customWidth="1"/>
@@ -1255,7 +1261,7 @@
     <col min="27" max="27" width="13" style="1" bestFit="1" customWidth="1"/>
     <col min="28" max="28" width="31" style="1" bestFit="1" customWidth="1"/>
     <col min="29" max="29" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="11.5" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="11.44140625" style="1" bestFit="1" customWidth="1"/>
     <col min="31" max="31" width="12" style="1" bestFit="1" customWidth="1"/>
     <col min="32" max="32" width="18" style="1" bestFit="1" customWidth="1"/>
     <col min="33" max="33" width="10" style="1" bestFit="1" customWidth="1"/>
@@ -1266,7 +1272,7 @@
     <col min="38" max="38" width="25" style="1" bestFit="1" customWidth="1"/>
     <col min="39" max="39" width="13" style="1" bestFit="1" customWidth="1"/>
     <col min="40" max="41" width="20" style="1" bestFit="1" customWidth="1"/>
-    <col min="42" max="42" width="13.125" style="1" bestFit="1" customWidth="1"/>
+    <col min="42" max="42" width="13.109375" style="1" bestFit="1" customWidth="1"/>
     <col min="43" max="43" width="10" style="1" bestFit="1" customWidth="1"/>
     <col min="44" max="47" width="13" style="1" bestFit="1" customWidth="1"/>
     <col min="48" max="48" width="14" style="1" bestFit="1" customWidth="1"/>
@@ -1275,10 +1281,10 @@
     <col min="51" max="51" width="16" style="1" bestFit="1" customWidth="1"/>
     <col min="52" max="52" width="19" style="1" bestFit="1" customWidth="1"/>
     <col min="53" max="53" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="54" max="54" width="11.5" style="1" bestFit="1" customWidth="1"/>
+    <col min="54" max="54" width="11.44140625" style="1" bestFit="1" customWidth="1"/>
     <col min="55" max="55" width="15" style="1" bestFit="1" customWidth="1"/>
-    <col min="56" max="56" width="11.5" style="1" bestFit="1" customWidth="1"/>
-    <col min="57" max="57" width="14.375" style="1" bestFit="1" customWidth="1"/>
+    <col min="56" max="56" width="11.44140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="57" max="57" width="14.33203125" style="1" bestFit="1" customWidth="1"/>
     <col min="58" max="58" width="17" style="1" bestFit="1" customWidth="1"/>
     <col min="59" max="59" width="11" style="1" bestFit="1" customWidth="1"/>
     <col min="60" max="60" width="21" style="1" bestFit="1" customWidth="1"/>
@@ -1290,7 +1296,7 @@
     <col min="67" max="67" width="5" style="1" bestFit="1" customWidth="1"/>
     <col min="68" max="68" width="17" style="1" bestFit="1" customWidth="1"/>
     <col min="69" max="69" width="18" style="1" bestFit="1" customWidth="1"/>
-    <col min="70" max="70" width="11.5" style="1" bestFit="1" customWidth="1"/>
+    <col min="70" max="70" width="11.44140625" style="1" bestFit="1" customWidth="1"/>
     <col min="71" max="71" width="13" style="1" bestFit="1" customWidth="1"/>
     <col min="72" max="72" width="10" style="1" bestFit="1" customWidth="1"/>
     <col min="73" max="73" width="6" style="1" bestFit="1" customWidth="1"/>
@@ -1323,7 +1329,7 @@
     <col min="103" max="103" width="11" style="1" bestFit="1" customWidth="1"/>
     <col min="104" max="104" width="15" style="1" bestFit="1" customWidth="1"/>
     <col min="105" max="105" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="106" max="107" width="11.5" style="1" bestFit="1" customWidth="1"/>
+    <col min="106" max="107" width="11.44140625" style="1" bestFit="1" customWidth="1"/>
     <col min="108" max="108" width="13" style="1" bestFit="1" customWidth="1"/>
     <col min="109" max="109" width="17" style="1" bestFit="1" customWidth="1"/>
     <col min="110" max="110" width="16" style="1" bestFit="1" customWidth="1"/>
@@ -1342,10 +1348,10 @@
     <col min="123" max="123" width="22" style="1" bestFit="1" customWidth="1"/>
     <col min="124" max="125" width="12" style="1" bestFit="1" customWidth="1"/>
     <col min="126" max="126" width="20" style="1" bestFit="1" customWidth="1"/>
-    <col min="127" max="130" width="11.5" style="1" bestFit="1" customWidth="1"/>
+    <col min="127" max="130" width="11.44140625" style="1" bestFit="1" customWidth="1"/>
     <col min="131" max="131" width="7" style="1" bestFit="1" customWidth="1"/>
     <col min="132" max="132" width="15" style="1" bestFit="1" customWidth="1"/>
-    <col min="133" max="133" width="11.5" style="1" bestFit="1" customWidth="1"/>
+    <col min="133" max="133" width="11.44140625" style="1" bestFit="1" customWidth="1"/>
     <col min="134" max="134" width="12" style="1" bestFit="1" customWidth="1"/>
     <col min="135" max="135" width="11" style="1" bestFit="1" customWidth="1"/>
     <col min="136" max="136" width="12" style="1" bestFit="1" customWidth="1"/>
@@ -1354,7 +1360,7 @@
     <col min="139" max="139" width="17" style="1" bestFit="1" customWidth="1"/>
     <col min="140" max="140" width="9" style="1" bestFit="1" customWidth="1"/>
     <col min="141" max="141" width="32" style="1" bestFit="1" customWidth="1"/>
-    <col min="142" max="142" width="11.5" style="1" bestFit="1" customWidth="1"/>
+    <col min="142" max="142" width="11.44140625" style="1" bestFit="1" customWidth="1"/>
     <col min="143" max="143" width="13" style="1" bestFit="1" customWidth="1"/>
     <col min="144" max="144" width="12" style="1" bestFit="1" customWidth="1"/>
     <col min="145" max="145" width="17" style="1" bestFit="1" customWidth="1"/>
@@ -1380,12 +1386,12 @@
     <col min="167" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:166">
+    <row r="1" spans="1:166" x14ac:dyDescent="0.3">
       <c r="A1" s="11" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:166">
+    <row r="2" spans="1:166" x14ac:dyDescent="0.3">
       <c r="A2" s="11" t="s">
         <v>1</v>
       </c>
@@ -1393,7 +1399,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:166">
+    <row r="3" spans="1:166" x14ac:dyDescent="0.3">
       <c r="A3" s="11" t="s">
         <v>3</v>
       </c>
@@ -1401,7 +1407,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:166">
+    <row r="4" spans="1:166" x14ac:dyDescent="0.3">
       <c r="A4" s="11" t="s">
         <v>5</v>
       </c>
@@ -1409,799 +1415,799 @@
         <v>6</v>
       </c>
     </row>
-    <row r="5" spans="1:166" s="9" customFormat="1" ht="38.25">
+    <row r="5" spans="1:166" s="9" customFormat="1" ht="41.4" x14ac:dyDescent="0.3">
       <c r="F5" s="9" t="s">
+        <v>236</v>
+      </c>
+      <c r="G5" s="9" t="s">
         <v>237</v>
       </c>
-      <c r="G5" s="9" t="s">
+      <c r="R5" s="10" t="s">
         <v>238</v>
       </c>
-      <c r="R5" s="10" t="s">
-        <v>239</v>
-      </c>
       <c r="S5" s="10" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="W5" s="9" t="s">
+        <v>239</v>
+      </c>
+      <c r="X5" s="9" t="s">
+        <v>239</v>
+      </c>
+      <c r="Y5" s="9" t="s">
+        <v>239</v>
+      </c>
+      <c r="Z5" s="9" t="s">
+        <v>239</v>
+      </c>
+      <c r="AA5" s="9" t="s">
+        <v>239</v>
+      </c>
+      <c r="AD5" s="9" t="s">
+        <v>239</v>
+      </c>
+      <c r="AE5" s="9" t="s">
+        <v>239</v>
+      </c>
+      <c r="AF5" s="9" t="s">
+        <v>239</v>
+      </c>
+      <c r="AG5" s="9" t="s">
+        <v>239</v>
+      </c>
+      <c r="AH5" s="9" t="s">
+        <v>239</v>
+      </c>
+      <c r="AI5" s="9" t="s">
+        <v>239</v>
+      </c>
+      <c r="AJ5" s="9" t="s">
+        <v>239</v>
+      </c>
+      <c r="AK5" s="9" t="s">
         <v>240</v>
       </c>
-      <c r="X5" s="9" t="s">
-        <v>240</v>
-      </c>
-      <c r="Y5" s="9" t="s">
-        <v>240</v>
-      </c>
-      <c r="Z5" s="9" t="s">
-        <v>240</v>
-      </c>
-      <c r="AA5" s="9" t="s">
-        <v>240</v>
-      </c>
-      <c r="AD5" s="9" t="s">
-        <v>240</v>
-      </c>
-      <c r="AE5" s="9" t="s">
-        <v>240</v>
-      </c>
-      <c r="AF5" s="9" t="s">
-        <v>240</v>
-      </c>
-      <c r="AG5" s="9" t="s">
-        <v>240</v>
-      </c>
-      <c r="AH5" s="9" t="s">
-        <v>240</v>
-      </c>
-      <c r="AI5" s="9" t="s">
-        <v>240</v>
-      </c>
-      <c r="AJ5" s="9" t="s">
-        <v>240</v>
-      </c>
-      <c r="AK5" s="9" t="s">
+      <c r="AL5" s="9" t="s">
+        <v>239</v>
+      </c>
+      <c r="AN5" s="9" t="s">
+        <v>239</v>
+      </c>
+      <c r="AO5" s="9" t="s">
+        <v>239</v>
+      </c>
+      <c r="AP5" s="9" t="s">
         <v>241</v>
       </c>
-      <c r="AL5" s="9" t="s">
-        <v>240</v>
-      </c>
-      <c r="AN5" s="9" t="s">
-        <v>240</v>
-      </c>
-      <c r="AO5" s="9" t="s">
-        <v>240</v>
-      </c>
-      <c r="AP5" s="9" t="s">
+      <c r="AS5" s="10" t="s">
         <v>242</v>
       </c>
-      <c r="AS5" s="10" t="s">
+      <c r="AT5" s="10" t="s">
+        <v>242</v>
+      </c>
+      <c r="AU5" s="10" t="s">
+        <v>242</v>
+      </c>
+      <c r="AW5" s="9" t="s">
+        <v>239</v>
+      </c>
+      <c r="BB5" s="9" t="s">
+        <v>239</v>
+      </c>
+      <c r="BC5" s="9" t="s">
+        <v>239</v>
+      </c>
+      <c r="BD5" s="9" t="s">
+        <v>239</v>
+      </c>
+      <c r="BE5" s="9" t="s">
+        <v>244</v>
+      </c>
+      <c r="BF5" s="9" t="s">
         <v>243</v>
       </c>
-      <c r="AT5" s="10" t="s">
-        <v>243</v>
-      </c>
-      <c r="AU5" s="10" t="s">
-        <v>243</v>
-      </c>
-      <c r="AW5" s="9" t="s">
-        <v>240</v>
-      </c>
-      <c r="BB5" s="9" t="s">
-        <v>240</v>
-      </c>
-      <c r="BC5" s="9" t="s">
-        <v>240</v>
-      </c>
-      <c r="BD5" s="9" t="s">
-        <v>240</v>
-      </c>
-      <c r="BE5" s="9" t="s">
+      <c r="BG5" s="9" t="s">
+        <v>239</v>
+      </c>
+      <c r="BH5" s="9" t="s">
+        <v>239</v>
+      </c>
+      <c r="BI5" s="9" t="s">
+        <v>239</v>
+      </c>
+      <c r="BJ5" s="9" t="s">
+        <v>239</v>
+      </c>
+      <c r="BK5" s="9" t="s">
+        <v>239</v>
+      </c>
+      <c r="BL5" s="9" t="s">
+        <v>239</v>
+      </c>
+      <c r="BM5" s="9" t="s">
+        <v>239</v>
+      </c>
+      <c r="BN5" s="9" t="s">
+        <v>239</v>
+      </c>
+      <c r="BO5" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="BP5" s="9" t="s">
+        <v>239</v>
+      </c>
+      <c r="BQ5" s="9" t="s">
+        <v>239</v>
+      </c>
+      <c r="BR5" s="9" t="s">
+        <v>239</v>
+      </c>
+      <c r="BS5" s="9" t="s">
         <v>245</v>
       </c>
-      <c r="BF5" s="9" t="s">
-        <v>244</v>
-      </c>
-      <c r="BG5" s="9" t="s">
-        <v>240</v>
-      </c>
-      <c r="BH5" s="9" t="s">
-        <v>240</v>
-      </c>
-      <c r="BI5" s="9" t="s">
-        <v>240</v>
-      </c>
-      <c r="BJ5" s="9" t="s">
-        <v>240</v>
-      </c>
-      <c r="BK5" s="9" t="s">
-        <v>240</v>
-      </c>
-      <c r="BL5" s="9" t="s">
-        <v>240</v>
-      </c>
-      <c r="BM5" s="9" t="s">
-        <v>240</v>
-      </c>
-      <c r="BN5" s="9" t="s">
-        <v>240</v>
-      </c>
-      <c r="BO5" s="9" t="s">
+      <c r="BT5" s="9" t="s">
+        <v>239</v>
+      </c>
+      <c r="BU5" s="9" t="s">
+        <v>239</v>
+      </c>
+      <c r="BV5" s="9" t="s">
+        <v>239</v>
+      </c>
+      <c r="BW5" s="9" t="s">
+        <v>239</v>
+      </c>
+      <c r="BX5" s="9" t="s">
+        <v>239</v>
+      </c>
+      <c r="BY5" s="9" t="s">
+        <v>239</v>
+      </c>
+      <c r="BZ5" s="9" t="s">
+        <v>239</v>
+      </c>
+      <c r="CA5" s="9" t="s">
+        <v>239</v>
+      </c>
+      <c r="CB5" s="9" t="s">
+        <v>239</v>
+      </c>
+      <c r="CC5" s="9" t="s">
+        <v>239</v>
+      </c>
+      <c r="CD5" s="9" t="s">
+        <v>239</v>
+      </c>
+      <c r="CJ5" s="9" t="s">
+        <v>239</v>
+      </c>
+      <c r="CK5" s="9" t="s">
+        <v>239</v>
+      </c>
+      <c r="CL5" s="9" t="s">
+        <v>239</v>
+      </c>
+      <c r="CN5" s="9" t="s">
+        <v>239</v>
+      </c>
+      <c r="CO5" s="9" t="s">
+        <v>239</v>
+      </c>
+      <c r="CP5" s="9" t="s">
+        <v>239</v>
+      </c>
+      <c r="CT5" s="9" t="s">
+        <v>239</v>
+      </c>
+      <c r="CU5" s="9" t="s">
+        <v>246</v>
+      </c>
+      <c r="CW5" s="9" t="s">
+        <v>239</v>
+      </c>
+      <c r="CX5" s="9" t="s">
+        <v>239</v>
+      </c>
+      <c r="CY5" s="9" t="s">
+        <v>239</v>
+      </c>
+      <c r="CZ5" s="9" t="s">
+        <v>239</v>
+      </c>
+      <c r="DA5" s="9" t="s">
+        <v>239</v>
+      </c>
+      <c r="DB5" s="9" t="s">
+        <v>239</v>
+      </c>
+      <c r="DC5" s="9" t="s">
+        <v>247</v>
+      </c>
+      <c r="DL5" s="9" t="s">
+        <v>239</v>
+      </c>
+      <c r="DM5" s="9" t="s">
+        <v>239</v>
+      </c>
+      <c r="DP5" s="9" t="s">
+        <v>248</v>
+      </c>
+      <c r="DR5" s="9" t="s">
+        <v>239</v>
+      </c>
+      <c r="DS5" s="9" t="s">
+        <v>239</v>
+      </c>
+      <c r="DW5" s="9" t="s">
+        <v>239</v>
+      </c>
+      <c r="DX5" s="9" t="s">
+        <v>239</v>
+      </c>
+      <c r="DY5" s="9" t="s">
+        <v>239</v>
+      </c>
+      <c r="DZ5" s="9" t="s">
+        <v>239</v>
+      </c>
+      <c r="EC5" s="9" t="s">
+        <v>239</v>
+      </c>
+      <c r="EE5" s="9" t="s">
+        <v>239</v>
+      </c>
+      <c r="EF5" s="9" t="s">
+        <v>239</v>
+      </c>
+      <c r="EG5" s="9" t="s">
+        <v>239</v>
+      </c>
+      <c r="EL5" s="9" t="s">
+        <v>239</v>
+      </c>
+      <c r="EM5" s="9" t="s">
+        <v>239</v>
+      </c>
+      <c r="EN5" s="9" t="s">
+        <v>239</v>
+      </c>
+      <c r="EO5" s="9" t="s">
+        <v>239</v>
+      </c>
+      <c r="EQ5" s="9" t="s">
+        <v>239</v>
+      </c>
+      <c r="ER5" s="9" t="s">
+        <v>239</v>
+      </c>
+      <c r="ES5" s="9" t="s">
+        <v>239</v>
+      </c>
+      <c r="EV5" s="9" t="s">
+        <v>239</v>
+      </c>
+      <c r="FH5" s="9" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="6" spans="1:166" s="8" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="7" t="s">
+        <v>249</v>
+      </c>
+      <c r="B6" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C6" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="D6" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="E6" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="F6" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="G6" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="H6" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="I6" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="J6" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="K6" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="L6" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="M6" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="N6" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="O6" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="P6" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q6" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="R6" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="S6" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="T6" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="U6" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="V6" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="W6" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="X6" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="Y6" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="Z6" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="AA6" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="AB6" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="AC6" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="AD6" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="AE6" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="AF6" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="AG6" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="AH6" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="AI6" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="AJ6" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="AK6" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="AL6" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="AM6" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="AN6" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="AO6" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="AP6" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="AQ6" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="AR6" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="AS6" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="AT6" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="AU6" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="AV6" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="AW6" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="AX6" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="AY6" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="AZ6" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="BA6" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="BB6" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="BC6" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="BD6" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="BE6" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="BF6" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="BG6" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="BH6" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="BI6" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="BJ6" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="BK6" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="BL6" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="BM6" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="BN6" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="BO6" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="BP6" s="7" t="s">
         <v>73</v>
       </c>
-      <c r="BP5" s="9" t="s">
-        <v>240</v>
-      </c>
-      <c r="BQ5" s="9" t="s">
-        <v>240</v>
-      </c>
-      <c r="BR5" s="9" t="s">
-        <v>240</v>
-      </c>
-      <c r="BS5" s="9" t="s">
-        <v>246</v>
-      </c>
-      <c r="BT5" s="9" t="s">
-        <v>240</v>
-      </c>
-      <c r="BU5" s="9" t="s">
-        <v>240</v>
-      </c>
-      <c r="BV5" s="9" t="s">
-        <v>240</v>
-      </c>
-      <c r="BW5" s="9" t="s">
-        <v>240</v>
-      </c>
-      <c r="BX5" s="9" t="s">
-        <v>240</v>
-      </c>
-      <c r="BY5" s="9" t="s">
-        <v>240</v>
-      </c>
-      <c r="BZ5" s="9" t="s">
-        <v>240</v>
-      </c>
-      <c r="CA5" s="9" t="s">
-        <v>240</v>
-      </c>
-      <c r="CB5" s="9" t="s">
-        <v>240</v>
-      </c>
-      <c r="CC5" s="9" t="s">
-        <v>240</v>
-      </c>
-      <c r="CD5" s="9" t="s">
-        <v>240</v>
-      </c>
-      <c r="CJ5" s="9" t="s">
-        <v>240</v>
-      </c>
-      <c r="CK5" s="9" t="s">
-        <v>240</v>
-      </c>
-      <c r="CL5" s="9" t="s">
-        <v>240</v>
-      </c>
-      <c r="CN5" s="9" t="s">
-        <v>240</v>
-      </c>
-      <c r="CO5" s="9" t="s">
-        <v>240</v>
-      </c>
-      <c r="CP5" s="9" t="s">
-        <v>240</v>
-      </c>
-      <c r="CT5" s="9" t="s">
-        <v>240</v>
-      </c>
-      <c r="CU5" s="9" t="s">
-        <v>247</v>
-      </c>
-      <c r="CW5" s="9" t="s">
-        <v>240</v>
-      </c>
-      <c r="CX5" s="9" t="s">
-        <v>240</v>
-      </c>
-      <c r="CY5" s="9" t="s">
-        <v>240</v>
-      </c>
-      <c r="CZ5" s="9" t="s">
-        <v>240</v>
-      </c>
-      <c r="DA5" s="9" t="s">
-        <v>240</v>
-      </c>
-      <c r="DB5" s="9" t="s">
-        <v>240</v>
-      </c>
-      <c r="DC5" s="9" t="s">
-        <v>248</v>
-      </c>
-      <c r="DL5" s="9" t="s">
-        <v>240</v>
-      </c>
-      <c r="DM5" s="9" t="s">
-        <v>240</v>
-      </c>
-      <c r="DP5" s="9" t="s">
-        <v>249</v>
-      </c>
-      <c r="DR5" s="9" t="s">
-        <v>240</v>
-      </c>
-      <c r="DS5" s="9" t="s">
-        <v>240</v>
-      </c>
-      <c r="DW5" s="9" t="s">
-        <v>240</v>
-      </c>
-      <c r="DX5" s="9" t="s">
-        <v>240</v>
-      </c>
-      <c r="DY5" s="9" t="s">
-        <v>240</v>
-      </c>
-      <c r="DZ5" s="9" t="s">
-        <v>240</v>
-      </c>
-      <c r="EC5" s="9" t="s">
-        <v>240</v>
-      </c>
-      <c r="EE5" s="9" t="s">
-        <v>240</v>
-      </c>
-      <c r="EF5" s="9" t="s">
-        <v>240</v>
-      </c>
-      <c r="EG5" s="9" t="s">
-        <v>240</v>
-      </c>
-      <c r="EL5" s="9" t="s">
-        <v>240</v>
-      </c>
-      <c r="EM5" s="9" t="s">
-        <v>240</v>
-      </c>
-      <c r="EN5" s="9" t="s">
-        <v>240</v>
-      </c>
-      <c r="EO5" s="9" t="s">
-        <v>240</v>
-      </c>
-      <c r="EQ5" s="9" t="s">
-        <v>240</v>
-      </c>
-      <c r="ER5" s="9" t="s">
-        <v>240</v>
-      </c>
-      <c r="ES5" s="9" t="s">
-        <v>240</v>
-      </c>
-      <c r="EV5" s="9" t="s">
-        <v>240</v>
-      </c>
-      <c r="FH5" s="9" t="s">
-        <v>240</v>
+      <c r="BQ6" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="BR6" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="BS6" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="BT6" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="BU6" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="BV6" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="BW6" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="BX6" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="BY6" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="BZ6" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="CA6" s="7" t="s">
+        <v>84</v>
+      </c>
+      <c r="CB6" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="CC6" s="7" t="s">
+        <v>86</v>
+      </c>
+      <c r="CD6" s="7" t="s">
+        <v>87</v>
+      </c>
+      <c r="CE6" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="CF6" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="CG6" s="7" t="s">
+        <v>90</v>
+      </c>
+      <c r="CH6" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="CI6" s="7" t="s">
+        <v>92</v>
+      </c>
+      <c r="CJ6" s="7" t="s">
+        <v>93</v>
+      </c>
+      <c r="CK6" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="CL6" s="7" t="s">
+        <v>95</v>
+      </c>
+      <c r="CM6" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="CN6" s="7" t="s">
+        <v>97</v>
+      </c>
+      <c r="CO6" s="7" t="s">
+        <v>98</v>
+      </c>
+      <c r="CP6" s="7" t="s">
+        <v>99</v>
+      </c>
+      <c r="CQ6" s="7" t="s">
+        <v>100</v>
+      </c>
+      <c r="CR6" s="7" t="s">
+        <v>101</v>
+      </c>
+      <c r="CS6" s="7" t="s">
+        <v>102</v>
+      </c>
+      <c r="CT6" s="7" t="s">
+        <v>103</v>
+      </c>
+      <c r="CU6" s="7" t="s">
+        <v>104</v>
+      </c>
+      <c r="CV6" s="7" t="s">
+        <v>105</v>
+      </c>
+      <c r="CW6" s="7" t="s">
+        <v>106</v>
+      </c>
+      <c r="CX6" s="7" t="s">
+        <v>106</v>
+      </c>
+      <c r="CY6" s="7" t="s">
+        <v>107</v>
+      </c>
+      <c r="CZ6" s="7" t="s">
+        <v>108</v>
+      </c>
+      <c r="DA6" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="DB6" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="DC6" s="7" t="s">
+        <v>111</v>
+      </c>
+      <c r="DD6" s="7" t="s">
+        <v>112</v>
+      </c>
+      <c r="DE6" s="7" t="s">
+        <v>113</v>
+      </c>
+      <c r="DF6" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="DG6" s="7" t="s">
+        <v>115</v>
+      </c>
+      <c r="DH6" s="7" t="s">
+        <v>116</v>
+      </c>
+      <c r="DI6" s="7" t="s">
+        <v>117</v>
+      </c>
+      <c r="DJ6" s="7" t="s">
+        <v>118</v>
+      </c>
+      <c r="DK6" s="7" t="s">
+        <v>119</v>
+      </c>
+      <c r="DL6" s="7" t="s">
+        <v>120</v>
+      </c>
+      <c r="DM6" s="7" t="s">
+        <v>121</v>
+      </c>
+      <c r="DN6" s="7" t="s">
+        <v>122</v>
+      </c>
+      <c r="DO6" s="7" t="s">
+        <v>123</v>
+      </c>
+      <c r="DP6" s="7" t="s">
+        <v>124</v>
+      </c>
+      <c r="DQ6" s="7" t="s">
+        <v>125</v>
+      </c>
+      <c r="DR6" s="7" t="s">
+        <v>126</v>
+      </c>
+      <c r="DS6" s="7" t="s">
+        <v>127</v>
+      </c>
+      <c r="DT6" s="7" t="s">
+        <v>128</v>
+      </c>
+      <c r="DU6" s="7" t="s">
+        <v>129</v>
+      </c>
+      <c r="DV6" s="7" t="s">
+        <v>130</v>
+      </c>
+      <c r="DW6" s="7" t="s">
+        <v>131</v>
+      </c>
+      <c r="DX6" s="7" t="s">
+        <v>132</v>
+      </c>
+      <c r="DY6" s="7" t="s">
+        <v>133</v>
+      </c>
+      <c r="DZ6" s="7" t="s">
+        <v>134</v>
+      </c>
+      <c r="EA6" s="7" t="s">
+        <v>135</v>
+      </c>
+      <c r="EB6" s="7" t="s">
+        <v>136</v>
+      </c>
+      <c r="EC6" s="7" t="s">
+        <v>137</v>
+      </c>
+      <c r="ED6" s="7" t="s">
+        <v>138</v>
+      </c>
+      <c r="EE6" s="7" t="s">
+        <v>139</v>
+      </c>
+      <c r="EF6" s="7" t="s">
+        <v>140</v>
+      </c>
+      <c r="EG6" s="7" t="s">
+        <v>141</v>
+      </c>
+      <c r="EH6" s="7" t="s">
+        <v>142</v>
+      </c>
+      <c r="EI6" s="7" t="s">
+        <v>143</v>
+      </c>
+      <c r="EJ6" s="7" t="s">
+        <v>144</v>
+      </c>
+      <c r="EK6" s="7" t="s">
+        <v>145</v>
+      </c>
+      <c r="EL6" s="7" t="s">
+        <v>146</v>
+      </c>
+      <c r="EM6" s="7" t="s">
+        <v>147</v>
+      </c>
+      <c r="EN6" s="7" t="s">
+        <v>148</v>
+      </c>
+      <c r="EO6" s="7" t="s">
+        <v>149</v>
+      </c>
+      <c r="EP6" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="EQ6" s="7" t="s">
+        <v>151</v>
+      </c>
+      <c r="ER6" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="ES6" s="7" t="s">
+        <v>153</v>
+      </c>
+      <c r="ET6" s="7" t="s">
+        <v>154</v>
+      </c>
+      <c r="EU6" s="7" t="s">
+        <v>155</v>
+      </c>
+      <c r="EV6" s="7" t="s">
+        <v>156</v>
+      </c>
+      <c r="EW6" s="7" t="s">
+        <v>157</v>
+      </c>
+      <c r="EX6" s="7" t="s">
+        <v>158</v>
+      </c>
+      <c r="EY6" s="7" t="s">
+        <v>159</v>
+      </c>
+      <c r="EZ6" s="7" t="s">
+        <v>160</v>
+      </c>
+      <c r="FA6" s="7" t="s">
+        <v>161</v>
+      </c>
+      <c r="FB6" s="7" t="s">
+        <v>162</v>
+      </c>
+      <c r="FC6" s="7" t="s">
+        <v>163</v>
+      </c>
+      <c r="FD6" s="7" t="s">
+        <v>164</v>
+      </c>
+      <c r="FE6" s="7" t="s">
+        <v>165</v>
+      </c>
+      <c r="FF6" s="7" t="s">
+        <v>166</v>
+      </c>
+      <c r="FG6" s="7" t="s">
+        <v>167</v>
+      </c>
+      <c r="FH6" s="7" t="s">
+        <v>168</v>
+      </c>
+      <c r="FI6" s="7" t="s">
+        <v>169</v>
+      </c>
+      <c r="FJ6" s="7" t="s">
+        <v>169</v>
       </c>
     </row>
-    <row r="6" spans="1:166" s="8" customFormat="1">
-      <c r="A6" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="B6" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="C6" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="D6" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="E6" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="F6" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="G6" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="H6" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="I6" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="J6" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="K6" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="L6" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="M6" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="N6" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="O6" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="P6" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="Q6" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="R6" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="S6" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="T6" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="U6" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="V6" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="W6" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="X6" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="Y6" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="Z6" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="AA6" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="AB6" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="AC6" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="AD6" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="AE6" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="AF6" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="AG6" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="AH6" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="AI6" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="AJ6" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="AK6" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="AL6" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="AM6" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="AN6" s="7" t="s">
-        <v>46</v>
-      </c>
-      <c r="AO6" s="7" t="s">
-        <v>47</v>
-      </c>
-      <c r="AP6" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="AQ6" s="7" t="s">
-        <v>49</v>
-      </c>
-      <c r="AR6" s="7" t="s">
-        <v>50</v>
-      </c>
-      <c r="AS6" s="7" t="s">
-        <v>51</v>
-      </c>
-      <c r="AT6" s="7" t="s">
-        <v>52</v>
-      </c>
-      <c r="AU6" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="AV6" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="AW6" s="7" t="s">
-        <v>55</v>
-      </c>
-      <c r="AX6" s="7" t="s">
-        <v>56</v>
-      </c>
-      <c r="AY6" s="7" t="s">
-        <v>57</v>
-      </c>
-      <c r="AZ6" s="7" t="s">
-        <v>58</v>
-      </c>
-      <c r="BA6" s="7" t="s">
-        <v>59</v>
-      </c>
-      <c r="BB6" s="7" t="s">
-        <v>60</v>
-      </c>
-      <c r="BC6" s="7" t="s">
-        <v>61</v>
-      </c>
-      <c r="BD6" s="7" t="s">
-        <v>62</v>
-      </c>
-      <c r="BE6" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="BF6" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="BG6" s="7" t="s">
-        <v>65</v>
-      </c>
-      <c r="BH6" s="7" t="s">
-        <v>66</v>
-      </c>
-      <c r="BI6" s="7" t="s">
-        <v>67</v>
-      </c>
-      <c r="BJ6" s="7" t="s">
-        <v>68</v>
-      </c>
-      <c r="BK6" s="7" t="s">
-        <v>69</v>
-      </c>
-      <c r="BL6" s="7" t="s">
-        <v>70</v>
-      </c>
-      <c r="BM6" s="7" t="s">
-        <v>71</v>
-      </c>
-      <c r="BN6" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="BO6" s="7" t="s">
-        <v>73</v>
-      </c>
-      <c r="BP6" s="7" t="s">
-        <v>74</v>
-      </c>
-      <c r="BQ6" s="7" t="s">
-        <v>75</v>
-      </c>
-      <c r="BR6" s="7" t="s">
-        <v>76</v>
-      </c>
-      <c r="BS6" s="7" t="s">
-        <v>77</v>
-      </c>
-      <c r="BT6" s="7" t="s">
-        <v>78</v>
-      </c>
-      <c r="BU6" s="7" t="s">
-        <v>79</v>
-      </c>
-      <c r="BV6" s="7" t="s">
-        <v>80</v>
-      </c>
-      <c r="BW6" s="7" t="s">
-        <v>81</v>
-      </c>
-      <c r="BX6" s="7" t="s">
-        <v>82</v>
-      </c>
-      <c r="BY6" s="7" t="s">
-        <v>83</v>
-      </c>
-      <c r="BZ6" s="7" t="s">
-        <v>84</v>
-      </c>
-      <c r="CA6" s="7" t="s">
-        <v>85</v>
-      </c>
-      <c r="CB6" s="7" t="s">
-        <v>86</v>
-      </c>
-      <c r="CC6" s="7" t="s">
-        <v>87</v>
-      </c>
-      <c r="CD6" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="CE6" s="7" t="s">
-        <v>89</v>
-      </c>
-      <c r="CF6" s="7" t="s">
-        <v>90</v>
-      </c>
-      <c r="CG6" s="7" t="s">
-        <v>91</v>
-      </c>
-      <c r="CH6" s="7" t="s">
-        <v>92</v>
-      </c>
-      <c r="CI6" s="7" t="s">
-        <v>93</v>
-      </c>
-      <c r="CJ6" s="7" t="s">
-        <v>94</v>
-      </c>
-      <c r="CK6" s="7" t="s">
-        <v>95</v>
-      </c>
-      <c r="CL6" s="7" t="s">
-        <v>96</v>
-      </c>
-      <c r="CM6" s="7" t="s">
-        <v>97</v>
-      </c>
-      <c r="CN6" s="7" t="s">
-        <v>98</v>
-      </c>
-      <c r="CO6" s="7" t="s">
-        <v>99</v>
-      </c>
-      <c r="CP6" s="7" t="s">
-        <v>100</v>
-      </c>
-      <c r="CQ6" s="7" t="s">
-        <v>101</v>
-      </c>
-      <c r="CR6" s="7" t="s">
-        <v>102</v>
-      </c>
-      <c r="CS6" s="7" t="s">
-        <v>103</v>
-      </c>
-      <c r="CT6" s="7" t="s">
-        <v>104</v>
-      </c>
-      <c r="CU6" s="7" t="s">
-        <v>105</v>
-      </c>
-      <c r="CV6" s="7" t="s">
-        <v>106</v>
-      </c>
-      <c r="CW6" s="7" t="s">
-        <v>107</v>
-      </c>
-      <c r="CX6" s="7" t="s">
-        <v>107</v>
-      </c>
-      <c r="CY6" s="7" t="s">
-        <v>108</v>
-      </c>
-      <c r="CZ6" s="7" t="s">
-        <v>109</v>
-      </c>
-      <c r="DA6" s="7" t="s">
-        <v>110</v>
-      </c>
-      <c r="DB6" s="7" t="s">
-        <v>111</v>
-      </c>
-      <c r="DC6" s="7" t="s">
-        <v>112</v>
-      </c>
-      <c r="DD6" s="7" t="s">
-        <v>113</v>
-      </c>
-      <c r="DE6" s="7" t="s">
-        <v>114</v>
-      </c>
-      <c r="DF6" s="7" t="s">
-        <v>115</v>
-      </c>
-      <c r="DG6" s="7" t="s">
-        <v>116</v>
-      </c>
-      <c r="DH6" s="7" t="s">
-        <v>117</v>
-      </c>
-      <c r="DI6" s="7" t="s">
-        <v>118</v>
-      </c>
-      <c r="DJ6" s="7" t="s">
-        <v>119</v>
-      </c>
-      <c r="DK6" s="7" t="s">
-        <v>120</v>
-      </c>
-      <c r="DL6" s="7" t="s">
-        <v>121</v>
-      </c>
-      <c r="DM6" s="7" t="s">
-        <v>122</v>
-      </c>
-      <c r="DN6" s="7" t="s">
-        <v>123</v>
-      </c>
-      <c r="DO6" s="7" t="s">
-        <v>124</v>
-      </c>
-      <c r="DP6" s="7" t="s">
-        <v>125</v>
-      </c>
-      <c r="DQ6" s="7" t="s">
-        <v>126</v>
-      </c>
-      <c r="DR6" s="7" t="s">
-        <v>127</v>
-      </c>
-      <c r="DS6" s="7" t="s">
-        <v>128</v>
-      </c>
-      <c r="DT6" s="7" t="s">
-        <v>129</v>
-      </c>
-      <c r="DU6" s="7" t="s">
-        <v>130</v>
-      </c>
-      <c r="DV6" s="7" t="s">
-        <v>131</v>
-      </c>
-      <c r="DW6" s="7" t="s">
-        <v>132</v>
-      </c>
-      <c r="DX6" s="7" t="s">
-        <v>133</v>
-      </c>
-      <c r="DY6" s="7" t="s">
-        <v>134</v>
-      </c>
-      <c r="DZ6" s="7" t="s">
-        <v>135</v>
-      </c>
-      <c r="EA6" s="7" t="s">
-        <v>136</v>
-      </c>
-      <c r="EB6" s="7" t="s">
-        <v>137</v>
-      </c>
-      <c r="EC6" s="7" t="s">
-        <v>138</v>
-      </c>
-      <c r="ED6" s="7" t="s">
-        <v>139</v>
-      </c>
-      <c r="EE6" s="7" t="s">
-        <v>140</v>
-      </c>
-      <c r="EF6" s="7" t="s">
-        <v>141</v>
-      </c>
-      <c r="EG6" s="7" t="s">
-        <v>142</v>
-      </c>
-      <c r="EH6" s="7" t="s">
-        <v>143</v>
-      </c>
-      <c r="EI6" s="7" t="s">
-        <v>144</v>
-      </c>
-      <c r="EJ6" s="7" t="s">
-        <v>145</v>
-      </c>
-      <c r="EK6" s="7" t="s">
-        <v>146</v>
-      </c>
-      <c r="EL6" s="7" t="s">
-        <v>147</v>
-      </c>
-      <c r="EM6" s="7" t="s">
-        <v>148</v>
-      </c>
-      <c r="EN6" s="7" t="s">
-        <v>149</v>
-      </c>
-      <c r="EO6" s="7" t="s">
-        <v>150</v>
-      </c>
-      <c r="EP6" s="7" t="s">
-        <v>151</v>
-      </c>
-      <c r="EQ6" s="7" t="s">
-        <v>152</v>
-      </c>
-      <c r="ER6" s="7" t="s">
-        <v>153</v>
-      </c>
-      <c r="ES6" s="7" t="s">
-        <v>154</v>
-      </c>
-      <c r="ET6" s="7" t="s">
-        <v>155</v>
-      </c>
-      <c r="EU6" s="7" t="s">
-        <v>156</v>
-      </c>
-      <c r="EV6" s="7" t="s">
-        <v>157</v>
-      </c>
-      <c r="EW6" s="7" t="s">
-        <v>158</v>
-      </c>
-      <c r="EX6" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="EY6" s="7" t="s">
-        <v>160</v>
-      </c>
-      <c r="EZ6" s="7" t="s">
-        <v>161</v>
-      </c>
-      <c r="FA6" s="7" t="s">
-        <v>162</v>
-      </c>
-      <c r="FB6" s="7" t="s">
-        <v>163</v>
-      </c>
-      <c r="FC6" s="7" t="s">
-        <v>164</v>
-      </c>
-      <c r="FD6" s="7" t="s">
-        <v>165</v>
-      </c>
-      <c r="FE6" s="7" t="s">
-        <v>166</v>
-      </c>
-      <c r="FF6" s="7" t="s">
-        <v>167</v>
-      </c>
-      <c r="FG6" s="7" t="s">
-        <v>168</v>
-      </c>
-      <c r="FH6" s="7" t="s">
-        <v>169</v>
-      </c>
-      <c r="FI6" s="7" t="s">
+    <row r="7" spans="1:166" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="2" t="s">
         <v>170</v>
       </c>
-      <c r="FJ6" s="7" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="7" spans="1:166" outlineLevel="1">
-      <c r="A7" s="2" t="s">
+      <c r="B7" s="2" t="s">
         <v>171</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="C7" s="2" t="s">
         <v>172</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="D7" s="2" t="s">
         <v>173</v>
       </c>
-      <c r="D7" s="2" t="s">
+      <c r="E7" s="2" t="s">
         <v>174</v>
       </c>
-      <c r="E7" s="2" t="s">
+      <c r="F7" s="2" t="s">
         <v>175</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>176</v>
       </c>
       <c r="G7" s="3">
         <v>46122</v>
@@ -2210,7 +2216,7 @@
         <v>1</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="J7" s="5">
         <v>10400</v>
@@ -2234,52 +2240,52 @@
         <v>10400</v>
       </c>
       <c r="Q7" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="R7" s="2" t="s">
         <v>178</v>
       </c>
-      <c r="R7" s="2" t="s">
+      <c r="S7" s="2" t="s">
         <v>179</v>
-      </c>
-      <c r="S7" s="2" t="s">
-        <v>180</v>
       </c>
       <c r="T7" s="2" t="s">
         <v>2</v>
       </c>
       <c r="U7" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="V7" s="2" t="s">
         <v>181</v>
       </c>
-      <c r="V7" s="2" t="s">
+      <c r="W7" s="2" t="s">
         <v>182</v>
       </c>
-      <c r="W7" s="2" t="s">
+      <c r="X7" s="2" t="s">
         <v>183</v>
       </c>
-      <c r="X7" s="2" t="s">
-        <v>184</v>
-      </c>
       <c r="Y7" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="Z7" s="2" t="s">
         <v>185</v>
       </c>
-      <c r="Z7" s="2" t="s">
+      <c r="AA7" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="AB7" s="2" t="s">
         <v>186</v>
       </c>
-      <c r="AA7" s="2" t="s">
-        <v>185</v>
-      </c>
-      <c r="AB7" s="2" t="s">
+      <c r="AC7" s="2" t="s">
         <v>187</v>
-      </c>
-      <c r="AC7" s="2" t="s">
-        <v>188</v>
       </c>
       <c r="AD7" s="6">
         <v>0</v>
       </c>
       <c r="AE7" s="2" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="AF7" s="2" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="AG7" s="6">
         <v>0</v>
@@ -2288,52 +2294,52 @@
         <v>0</v>
       </c>
       <c r="AI7" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="AJ7" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="AK7" s="2" t="s">
         <v>189</v>
-      </c>
-      <c r="AJ7" s="2" t="s">
-        <v>189</v>
-      </c>
-      <c r="AK7" s="2" t="s">
-        <v>190</v>
       </c>
       <c r="AL7" s="3">
         <v>45365</v>
       </c>
       <c r="AM7" s="2" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="AN7" s="2" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="AO7" s="2" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="AP7" s="3">
         <v>46144</v>
       </c>
       <c r="AQ7" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="AR7" s="2" t="s">
         <v>192</v>
       </c>
-      <c r="AR7" s="2" t="s">
+      <c r="AS7" s="2" t="s">
         <v>193</v>
       </c>
-      <c r="AS7" s="2" t="s">
+      <c r="AT7" s="2" t="s">
         <v>194</v>
       </c>
-      <c r="AT7" s="2" t="s">
+      <c r="AU7" s="2" t="s">
         <v>195</v>
       </c>
-      <c r="AU7" s="2" t="s">
+      <c r="AV7" s="2" t="s">
         <v>196</v>
       </c>
-      <c r="AV7" s="2" t="s">
+      <c r="AW7" s="2" t="s">
         <v>197</v>
       </c>
-      <c r="AW7" s="2" t="s">
+      <c r="AX7" s="2" t="s">
         <v>198</v>
-      </c>
-      <c r="AX7" s="2" t="s">
-        <v>199</v>
       </c>
       <c r="AY7" s="5">
         <v>10400</v>
@@ -2342,42 +2348,42 @@
         <v>10400</v>
       </c>
       <c r="BA7" s="2" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="BB7" s="6">
         <v>0</v>
       </c>
       <c r="BC7" s="2" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="BD7" s="2" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="BE7" s="3">
         <v>46141</v>
       </c>
       <c r="BF7" s="2" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="BG7" s="2" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="BH7" s="3"/>
       <c r="BI7" s="2" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="BJ7" s="3"/>
       <c r="BK7" s="2" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="BL7" s="6">
         <v>0</v>
       </c>
       <c r="BM7" s="2" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="BN7" s="2" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="BO7" s="6">
         <v>0</v>
@@ -2389,10 +2395,10 @@
         <v>0</v>
       </c>
       <c r="BR7" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="BS7" s="2" t="s">
         <v>201</v>
-      </c>
-      <c r="BS7" s="2" t="s">
-        <v>202</v>
       </c>
       <c r="BT7" s="6">
         <v>0</v>
@@ -2410,67 +2416,67 @@
         <v>0</v>
       </c>
       <c r="BY7" s="2" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="BZ7" s="2" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="CA7" s="2" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="CB7" s="2" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="CC7" s="6">
         <v>0</v>
       </c>
       <c r="CD7" s="2" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="CE7" s="2" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="CF7" s="3">
         <v>46141</v>
       </c>
       <c r="CG7" s="2" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="CH7" s="2" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="CI7" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="CJ7" s="2" t="s">
         <v>204</v>
       </c>
-      <c r="CJ7" s="2" t="s">
+      <c r="CK7" s="2" t="s">
         <v>205</v>
       </c>
-      <c r="CK7" s="2" t="s">
+      <c r="CL7" s="2" t="s">
         <v>206</v>
       </c>
-      <c r="CL7" s="2" t="s">
+      <c r="CM7" s="2" t="s">
         <v>207</v>
       </c>
-      <c r="CM7" s="2" t="s">
+      <c r="CN7" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="CO7" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="CP7" s="2" t="s">
         <v>208</v>
       </c>
-      <c r="CN7" s="2" t="s">
-        <v>185</v>
-      </c>
-      <c r="CO7" s="2" t="s">
-        <v>185</v>
-      </c>
-      <c r="CP7" s="2" t="s">
+      <c r="CQ7" s="2" t="s">
         <v>209</v>
       </c>
-      <c r="CQ7" s="2" t="s">
+      <c r="CR7" s="2" t="s">
         <v>210</v>
       </c>
-      <c r="CR7" s="2" t="s">
+      <c r="CS7" s="2" t="s">
         <v>211</v>
-      </c>
-      <c r="CS7" s="2" t="s">
-        <v>212</v>
       </c>
       <c r="CT7" s="6">
         <v>0</v>
@@ -2479,16 +2485,16 @@
         <v>15104</v>
       </c>
       <c r="CV7" s="2" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="CW7" s="2" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="CX7" s="2" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="CY7" s="2" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="CZ7" s="6">
         <v>1</v>
@@ -2497,95 +2503,95 @@
         <v>0</v>
       </c>
       <c r="DB7" s="2" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="DC7" s="2" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="DD7" s="5">
         <v>10400</v>
       </c>
       <c r="DE7" s="2" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="DF7" s="2" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="DG7" s="3">
         <v>46119</v>
       </c>
       <c r="DH7" s="2" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="DI7" s="6">
         <v>0</v>
       </c>
       <c r="DJ7" s="2" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="DK7" s="6">
         <v>0</v>
       </c>
       <c r="DL7" s="3"/>
       <c r="DM7" s="2" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="DN7" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="DO7" s="2" t="s">
         <v>215</v>
       </c>
-      <c r="DO7" s="2" t="s">
+      <c r="DP7" s="2" t="s">
         <v>216</v>
-      </c>
-      <c r="DP7" s="2" t="s">
-        <v>217</v>
       </c>
       <c r="DQ7" s="3">
         <v>46141</v>
       </c>
       <c r="DR7" s="2" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="DS7" s="2" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="DT7" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="DU7" s="2" t="s">
         <v>218</v>
       </c>
-      <c r="DU7" s="2" t="s">
+      <c r="DV7" s="2" t="s">
         <v>219</v>
       </c>
-      <c r="DV7" s="2" t="s">
+      <c r="DW7" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="DX7" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="DY7" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="DZ7" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="EA7" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="EB7" s="2" t="s">
         <v>220</v>
-      </c>
-      <c r="DW7" s="2" t="s">
-        <v>185</v>
-      </c>
-      <c r="DX7" s="2" t="s">
-        <v>185</v>
-      </c>
-      <c r="DY7" s="2" t="s">
-        <v>185</v>
-      </c>
-      <c r="DZ7" s="2" t="s">
-        <v>185</v>
-      </c>
-      <c r="EA7" s="2" t="s">
-        <v>188</v>
-      </c>
-      <c r="EB7" s="2" t="s">
-        <v>221</v>
       </c>
       <c r="EC7" s="6">
         <v>0</v>
       </c>
       <c r="ED7" s="2" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="EE7" s="2" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="EF7" s="2" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="EG7" s="6">
         <v>0</v>
@@ -2594,88 +2600,88 @@
         <v>18</v>
       </c>
       <c r="EI7" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="EJ7" s="2" t="s">
         <v>223</v>
       </c>
-      <c r="EJ7" s="2" t="s">
+      <c r="EK7" s="2" t="s">
         <v>224</v>
       </c>
-      <c r="EK7" s="2" t="s">
+      <c r="EL7" s="2" t="s">
         <v>225</v>
-      </c>
-      <c r="EL7" s="2" t="s">
-        <v>226</v>
       </c>
       <c r="EM7" s="6">
         <v>0</v>
       </c>
       <c r="EN7" s="2" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="EO7" s="2" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="EP7" s="2" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="EQ7" s="6">
         <v>0</v>
       </c>
       <c r="ER7" s="2" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="ES7" s="2" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="ET7" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="EU7" s="2" t="s">
         <v>228</v>
       </c>
-      <c r="EU7" s="2" t="s">
+      <c r="EV7" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="EW7" s="2" t="s">
         <v>229</v>
       </c>
-      <c r="EV7" s="2" t="s">
-        <v>185</v>
-      </c>
-      <c r="EW7" s="2" t="s">
+      <c r="EX7" s="2" t="s">
         <v>230</v>
       </c>
-      <c r="EX7" s="2" t="s">
+      <c r="EY7" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="EZ7" s="2" t="s">
         <v>231</v>
       </c>
-      <c r="EY7" s="2" t="s">
-        <v>185</v>
-      </c>
-      <c r="EZ7" s="2" t="s">
+      <c r="FA7" s="2" t="s">
         <v>232</v>
       </c>
-      <c r="FA7" s="2" t="s">
+      <c r="FB7" s="2" t="s">
         <v>233</v>
       </c>
-      <c r="FB7" s="2" t="s">
+      <c r="FC7" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="FD7" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="FE7" s="2" t="s">
         <v>234</v>
       </c>
-      <c r="FC7" s="2" t="s">
-        <v>188</v>
-      </c>
-      <c r="FD7" s="2" t="s">
-        <v>221</v>
-      </c>
-      <c r="FE7" s="2" t="s">
+      <c r="FF7" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="FG7" s="2" t="s">
+        <v>229</v>
+      </c>
+      <c r="FH7" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="FI7" s="2" t="s">
         <v>235</v>
       </c>
-      <c r="FF7" s="2" t="s">
-        <v>172</v>
-      </c>
-      <c r="FG7" s="2" t="s">
-        <v>230</v>
-      </c>
-      <c r="FH7" s="2" t="s">
-        <v>185</v>
-      </c>
-      <c r="FI7" s="2" t="s">
-        <v>236</v>
-      </c>
       <c r="FJ7" s="2" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
     </row>
   </sheetData>
